--- a/test/tdspayment.xlsx
+++ b/test/tdspayment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26AD86C-6D83-468A-8B62-C877D72CBB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7821E0-7E2C-4F60-A17F-A6A6BA487BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{61E9A8C4-EA73-4E25-BFAB-48B3BC869182}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Vaishnavi</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>193 - Interest on securities</t>
+  </si>
+  <si>
+    <t>ASDFG7</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
         <v>37196</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>7412</v>
